--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_67652_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_67652_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R7b5546f44878404f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5c5c420b7f744863"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3196</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3418</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4525</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3861</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2311</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2754</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2532</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8835</x:v>
+        <x:v>      0.3197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8171</x:v>
+        <x:v>      0.2754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9056</x:v>
+        <x:v>      0.1868</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7949</x:v>
+        <x:v>      0.2754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7728</x:v>
+        <x:v>      0.2754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7728</x:v>
+        <x:v>      0.2754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9277</x:v>
+        <x:v>      0.3197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8171</x:v>
+        <x:v>      0.3197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8613</x:v>
+        <x:v>      0.2311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6842</x:v>
+        <x:v>      0.2311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8392</x:v>
+        <x:v>      0.1868</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7728</x:v>
+        <x:v>      0.3197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8171</x:v>
+        <x:v>      0.2754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8392</x:v>
+        <x:v>      0.3197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8613</x:v>
+        <x:v>      0.2311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8171</x:v>
+        <x:v>      0.2311</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9277</x:v>
+        <x:v>      0.4525</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +819,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8613</x:v>
+        <x:v>      0.2754</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7949</x:v>
+        <x:v>      0.3197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8613</x:v>
+        <x:v>      0.3197</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8392</x:v>
+        <x:v>      0.3639</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_67652_completo.xlsx
+++ b/132_Cuenca_Quilca_-_Vitor_-_Chili/_raw_reportes_xlsx/IDConfig_67652_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5c5c420b7f744863"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbb868030c13049c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1662</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1821</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2484</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2484</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3877</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2484</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1741</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1662</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4109</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3181</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4341</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2717</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4109</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1788</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3645</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3196</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3418</x:v>
+        <x:v>      0.3413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3418</x:v>
+        <x:v>      0.3413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4525</x:v>
+        <x:v>      0.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3861</x:v>
+        <x:v>      0.3877</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2532</x:v>
+        <x:v>      0.2484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1823</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3639</x:v>
+        <x:v>      0.3645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2975</x:v>
+        <x:v>      0.2949</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4303</x:v>
+        <x:v>      0.4341</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3196</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1868</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1868</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4525</x:v>
+        <x:v>      0.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3639</x:v>
+        <x:v>      0.3645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4074</x:v>
+        <x:v>      0.3645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3384</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3154</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4304</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2924</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3614</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4764</x:v>
+        <x:v>      0.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3844</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4525</x:v>
+        <x:v>      0.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3844</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4967</x:v>
+        <x:v>      0.5037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4074</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2924</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3614</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4764</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3844</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3844</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4534</x:v>
+        <x:v>      0.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4534</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3844</x:v>
+        <x:v>      0.3645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3614</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1772</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1723</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4304</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1675</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1772</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3844</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1723</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2004</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1675</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1675</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1772</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2004</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3154</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4304</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2234</x:v>
+        <x:v>      0.1182</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1626</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1868</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1772</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1723</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3154</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2924</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1578</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1675</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1723</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2924</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2924</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1772</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1772</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1772</x:v>
+        <x:v>      0.1182</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1626</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2234</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1578</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2694</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1626</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1660</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4074</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3154</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2924</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2464</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1675</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1675</x:v>
+        <x:v>      0.1342</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2234</x:v>
+        <x:v>      0.1788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3154</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1774</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1626</x:v>
+        <x:v>      0.1502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +2994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3154</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +3009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4967</x:v>
+        <x:v>      0.5037</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +3024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +3039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4525</x:v>
+        <x:v>      0.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +3054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5454</x:v>
+        <x:v>      0.5501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +3069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4082</x:v>
+        <x:v>      0.4109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +3084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4534</x:v>
+        <x:v>      0.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +3099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4304</x:v>
+        <x:v>      0.3645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +3114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4994</x:v>
+        <x:v>      0.4573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +3144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6897</x:v>
+        <x:v>      0.5501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +3174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4746</x:v>
+        <x:v>      0.4805</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3639</x:v>
+        <x:v>      0.3645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2975</x:v>
+        <x:v>      0.2949</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1675</x:v>
+        <x:v>      0.1662</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3384</x:v>
+        <x:v>      0.2484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4994</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2311</x:v>
+        <x:v>      0.2252</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2532</x:v>
+        <x:v>      0.2484</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2754</x:v>
+        <x:v>      0.2717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3639</x:v>
+        <x:v>      0.3645</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3197</x:v>
+        <x:v>      0.3181</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3418</x:v>
+        <x:v>      0.3413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3418</x:v>
+        <x:v>      0.3413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3418</x:v>
+        <x:v>      0.3413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5410</x:v>
+        <x:v>      0.5501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5410</x:v>
+        <x:v>      0.5501</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +3579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      1.9917</x:v>
+        <x:v>      1.8555</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +3609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2471</x:v>
+        <x:v>      2.4938</x:v>
       </x:c>
     </x:row>
     <x:row>
